--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>_id</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>福利任务</t>
+  </si>
+  <si>
+    <t>节日任务</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1032,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E20"/>
+  <dimension ref="C3:E21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1175,6 +1178,17 @@
         <v>20</v>
       </c>
     </row>
+    <row r="21" customHeight="1" spans="3:5">
+      <c r="C21" s="1">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
